--- a/src/FileCabinet/SuiteScripts/Nkn/xlsx/scv_tmpl_wbs_import.xlsx
+++ b/src/FileCabinet/SuiteScripts/Nkn/xlsx/scv_tmpl_wbs_import.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="28">
   <si>
     <t>Key</t>
   </si>
@@ -99,6 +99,12 @@
   </si>
   <si>
     <t>YYYY-MM-DD</t>
+  </si>
+  <si>
+    <t>Unit</t>
+  </si>
+  <si>
+    <t>Units of item</t>
   </si>
 </sst>
 </file>
@@ -447,19 +453,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:L3"/>
+  <dimension ref="A1:M3"/>
   <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16" style="3" customWidth="1"/>
     <col min="3" max="3" width="28" style="3" customWidth="1"/>
     <col min="4" max="4" width="24" style="3" customWidth="1"/>
     <col min="5" max="6" width="22" style="3" customWidth="1"/>
-    <col min="7" max="10" width="14" style="3" customWidth="1"/>
-    <col min="11" max="12" width="16" style="3" customWidth="1"/>
-    <col min="13" max="16384" width="12.5703125" style="3"/>
+    <col min="7" max="7" width="9.28515625" style="3" customWidth="1"/>
+    <col min="8" max="11" width="14" style="3" customWidth="1"/>
+    <col min="12" max="13" width="16" style="3" customWidth="1"/>
+    <col min="14" max="16384" width="12.5703125" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -479,25 +486,28 @@
         <v>5</v>
       </c>
       <c r="G1" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="H1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:12" ht="89.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:13" ht="89.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>12</v>
       </c>
@@ -520,22 +530,25 @@
         <v>14</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I2" s="2" t="s">
         <v>15</v>
       </c>
       <c r="J2" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="K2" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="K2" s="2" t="s">
+      <c r="L2" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="L2" s="2" t="s">
+      <c r="M2" s="2" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="3" spans="1:12" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:13" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>19</v>
       </c>
@@ -555,17 +568,20 @@
         <v>23</v>
       </c>
       <c r="G3" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="H3" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="H3" s="2"/>
       <c r="I3" s="2"/>
-      <c r="J3" s="2" t="s">
+      <c r="J3" s="2"/>
+      <c r="K3" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="K3" s="2" t="s">
+      <c r="L3" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="L3" s="2" t="s">
+      <c r="M3" s="2" t="s">
         <v>15</v>
       </c>
     </row>
